--- a/РАБОЧИЙ СТОЛ/расчеты Останкино КИ/дв 10,08,26 лгрсч ост ки.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино КИ/дв 10,08,26 лгрсч ост ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63A4BD77-EB9F-4DC9-BD10-A4FCCB3C9F1A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBC6393F-AA26-4669-8F3E-1732EDFFE539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,15 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AE$103</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -616,7 +608,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -631,7 +623,6 @@
     <xf numFmtId="164" fontId="1" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1725,7 +1716,7 @@
         <v>137.0042</v>
       </c>
       <c r="Q9" s="5">
-        <f t="shared" ref="Q7:Q29" si="7">15*P9-O9-F9</f>
+        <f t="shared" ref="Q9:Q29" si="7">15*P9-O9-F9</f>
         <v>587.48800000000006</v>
       </c>
       <c r="R9" s="1">
@@ -4647,7 +4638,7 @@
         <v>27.2</v>
       </c>
       <c r="Q36" s="5">
-        <f t="shared" ref="Q36:Q54" si="8">15*P36-O36-F36</f>
+        <f t="shared" ref="Q36:Q53" si="8">15*P36-O36-F36</f>
         <v>202</v>
       </c>
       <c r="R36" s="1">
@@ -7030,7 +7021,7 @@
         <v>9.2843999999999998</v>
       </c>
       <c r="Q58" s="5">
-        <f t="shared" ref="Q57:Q61" si="14">15*P58-O58-F58</f>
+        <f t="shared" ref="Q58:Q61" si="14">15*P58-O58-F58</f>
         <v>26.984999999999992</v>
       </c>
       <c r="R58" s="1">
@@ -7095,7 +7086,7 @@
       <c r="AV58" s="1"/>
     </row>
     <row r="59" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A59" s="14" t="s">
+      <c r="A59" s="1" t="s">
         <v>102</v>
       </c>
       <c r="B59" s="1" t="s">
@@ -8366,7 +8357,7 @@
       <c r="AC70" s="1">
         <v>12.6</v>
       </c>
-      <c r="AD70" s="15" t="s">
+      <c r="AD70" s="14" t="s">
         <v>155</v>
       </c>
       <c r="AE70" s="1">
@@ -10219,7 +10210,7 @@
       <c r="AV87" s="1"/>
     </row>
     <row r="88" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A88" s="14" t="s">
+      <c r="A88" s="1" t="s">
         <v>136</v>
       </c>
       <c r="B88" s="1" t="s">
@@ -10663,7 +10654,7 @@
         <v>28.6</v>
       </c>
       <c r="Q92" s="5">
-        <f t="shared" ref="Q92:Q93" si="22">15*P92-O92-F92</f>
+        <f t="shared" ref="Q92" si="22">15*P92-O92-F92</f>
         <v>240</v>
       </c>
       <c r="R92" s="1">
@@ -11076,7 +11067,7 @@
         <v>14.6</v>
       </c>
       <c r="Q96" s="5">
-        <f t="shared" ref="Q96:Q103" si="23">15*P96-O96-F96</f>
+        <f t="shared" ref="Q96:Q101" si="23">15*P96-O96-F96</f>
         <v>98</v>
       </c>
       <c r="R96" s="1">
@@ -11729,7 +11720,7 @@
         <v>48</v>
       </c>
       <c r="L102" s="1">
-        <f t="shared" ref="L102:L133" si="25">E102-K102</f>
+        <f t="shared" ref="L102:L103" si="25">E102-K102</f>
         <v>-6</v>
       </c>
       <c r="M102" s="1"/>
@@ -11743,7 +11734,7 @@
       </c>
       <c r="Q102" s="5"/>
       <c r="R102" s="1">
-        <f t="shared" ref="R102:R133" si="26">(F102+O102+Q102)/P102</f>
+        <f t="shared" ref="R102:R103" si="26">(F102+O102+Q102)/P102</f>
         <v>23.80952380952381</v>
       </c>
       <c r="S102" s="1">
